--- a/output/pharma_nordic_example_nodes.xlsx
+++ b/output/pharma_nordic_example_nodes.xlsx
@@ -532,7 +532,7 @@
         <v>0.2339622641509434</v>
       </c>
       <c r="P2">
-        <v>0.1627043167340302</v>
+        <v>0.1627043167340306</v>
       </c>
       <c r="Q2">
         <v>0.6566840277777779</v>
@@ -609,7 +609,7 @@
         <v>0.223826714801444</v>
       </c>
       <c r="P3">
-        <v>0.1979348761526406</v>
+        <v>0.1979348761526409</v>
       </c>
       <c r="Q3">
         <v>0.4583333333333333</v>
@@ -686,7 +686,7 @@
         <v>0.3625730994152047</v>
       </c>
       <c r="P4">
-        <v>0.2056428338727415</v>
+        <v>0.2056428338727418</v>
       </c>
       <c r="Q4">
         <v>0.1773469387755102</v>
@@ -780,7 +780,7 @@
         <v>0.2123287671232877</v>
       </c>
       <c r="P5">
-        <v>0.00315419079394505</v>
+        <v>0.003154190793945012</v>
       </c>
       <c r="Q5">
         <v>1</v>
@@ -877,7 +877,7 @@
         <v>0.2683982683982684</v>
       </c>
       <c r="P6">
-        <v>0.01557029016105791</v>
+        <v>0.0155702901610576</v>
       </c>
       <c r="Q6">
         <v>0.2401</v>
@@ -907,7 +907,7 @@
         <v>5</v>
       </c>
       <c r="Z6">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AA6">
         <v>3</v>
@@ -974,7 +974,7 @@
         <v>0.223021582733813</v>
       </c>
       <c r="P7">
-        <v>0.005855458830191579</v>
+        <v>0.005855458830191469</v>
       </c>
       <c r="Q7">
         <v>0.305</v>
@@ -1004,7 +1004,7 @@
         <v>9</v>
       </c>
       <c r="Z7">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AA7">
         <v>5</v>
@@ -1071,7 +1071,7 @@
         <v>0.1828908554572271</v>
       </c>
       <c r="P8">
-        <v>0.001186184338600638</v>
+        <v>0.001186184338600607</v>
       </c>
       <c r="Q8">
         <v>1</v>
@@ -1101,7 +1101,7 @@
         <v>39</v>
       </c>
       <c r="Z8">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AA8">
         <v>1</v>
@@ -1168,7 +1168,7 @@
         <v>0.2052980132450331</v>
       </c>
       <c r="P9">
-        <v>0.00475348470433302</v>
+        <v>0.004753484704332955</v>
       </c>
       <c r="Q9">
         <v>0.8890306122448979</v>
@@ -1198,7 +1198,7 @@
         <v>36</v>
       </c>
       <c r="Z9">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="AA9">
         <v>15</v>
@@ -1265,7 +1265,7 @@
         <v>0.2052980132450331</v>
       </c>
       <c r="P10">
-        <v>0.004753484704333016</v>
+        <v>0.00475348470433297</v>
       </c>
       <c r="Q10">
         <v>0.8890306122448979</v>
@@ -1362,7 +1362,7 @@
         <v>0.1861861861861862</v>
       </c>
       <c r="P11">
-        <v>0.002771926326836752</v>
+        <v>0.002771926326836659</v>
       </c>
       <c r="Q11">
         <v>0.9225</v>
@@ -1439,7 +1439,7 @@
         <v>0.248</v>
       </c>
       <c r="P12">
-        <v>0.4792480623402842</v>
+        <v>0.4792480623402848</v>
       </c>
       <c r="Q12">
         <v>0.4073600481859411</v>
@@ -1527,7 +1527,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="P13">
-        <v>0.02413727288602275</v>
+        <v>0.02413727288602273</v>
       </c>
       <c r="Q13">
         <v>0.7402469135802467</v>
@@ -1624,7 +1624,7 @@
         <v>0.2339622641509434</v>
       </c>
       <c r="P14">
-        <v>0.2745492459451341</v>
+        <v>0.2745492459451345</v>
       </c>
       <c r="Q14">
         <v>0.7469444444444444</v>
@@ -1701,7 +1701,7 @@
         <v>0.2271062271062271</v>
       </c>
       <c r="P15">
-        <v>0.01091136045999155</v>
+        <v>0.01091136045999138</v>
       </c>
       <c r="Q15">
         <v>0.3401000000000001</v>
@@ -1731,7 +1731,7 @@
         <v>10</v>
       </c>
       <c r="Z15">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AA15">
         <v>7</v>
@@ -1875,7 +1875,7 @@
         <v>0.256198347107438</v>
       </c>
       <c r="P17">
-        <v>0.5186239472089466</v>
+        <v>0.5186239472089471</v>
       </c>
       <c r="Q17">
         <v>0.4151929209183673</v>
@@ -1966,7 +1966,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="P18">
-        <v>0.04986997364462011</v>
+        <v>0.04986997364462014</v>
       </c>
       <c r="Q18">
         <v>0.9027777777777779</v>
@@ -1996,7 +1996,7 @@
         <v>37</v>
       </c>
       <c r="Z18">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AA18">
         <v>15</v>
@@ -2063,7 +2063,7 @@
         <v>0.2145328719723184</v>
       </c>
       <c r="P19">
-        <v>0.04448123221594933</v>
+        <v>0.04448123221594937</v>
       </c>
       <c r="Q19">
         <v>0.6111111111111112</v>
@@ -2140,7 +2140,7 @@
         <v>0.3195876288659794</v>
       </c>
       <c r="P20">
-        <v>0.05378569674578806</v>
+        <v>0.05378569674578799</v>
       </c>
       <c r="Q20">
         <v>0.2622448979591837</v>
@@ -2237,7 +2237,7 @@
         <v>0.2897196261682243</v>
       </c>
       <c r="P21">
-        <v>0.1019516679235184</v>
+        <v>0.1019516679235185</v>
       </c>
       <c r="Q21">
         <v>0.4822530864197531</v>
@@ -2331,7 +2331,7 @@
         <v>0.248</v>
       </c>
       <c r="P22">
-        <v>0.02689303999999576</v>
+        <v>0.02689303999999563</v>
       </c>
       <c r="Q22">
         <v>0.3792</v>
@@ -2408,7 +2408,7 @@
         <v>0.1861861861861862</v>
       </c>
       <c r="P23">
-        <v>0.002771926326836764</v>
+        <v>0.002771926326836658</v>
       </c>
       <c r="Q23">
         <v>0.9225</v>
@@ -2438,7 +2438,7 @@
         <v>38</v>
       </c>
       <c r="Z23">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="AA23">
         <v>15</v>
@@ -2505,7 +2505,7 @@
         <v>0.2123287671232877</v>
       </c>
       <c r="P24">
-        <v>0.003154190793945055</v>
+        <v>0.003154190793944997</v>
       </c>
       <c r="Q24">
         <v>1</v>
@@ -2535,7 +2535,7 @@
         <v>39</v>
       </c>
       <c r="Z24">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="AA24">
         <v>1</v>
@@ -2676,7 +2676,7 @@
         <v>0.25</v>
       </c>
       <c r="P26">
-        <v>0.01468630870620834</v>
+        <v>0.01468630870620831</v>
       </c>
       <c r="Q26">
         <v>0.686530612244898</v>
@@ -2706,7 +2706,7 @@
         <v>28</v>
       </c>
       <c r="Z26">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA26">
         <v>15</v>
@@ -2773,7 +2773,7 @@
         <v>0.1776504297994269</v>
       </c>
       <c r="P27">
-        <v>0.01130002982502728</v>
+        <v>0.01130002982502724</v>
       </c>
       <c r="Q27">
         <v>1.006944444444444</v>
@@ -2803,7 +2803,7 @@
         <v>40</v>
       </c>
       <c r="Z27">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AA27">
         <v>15</v>
@@ -2867,7 +2867,7 @@
         <v>0.1776504297994269</v>
       </c>
       <c r="P28">
-        <v>0.01130002982502729</v>
+        <v>0.01130002982502725</v>
       </c>
       <c r="Q28">
         <v>1.006944444444444</v>
@@ -2897,7 +2897,7 @@
         <v>40</v>
       </c>
       <c r="Z28">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AA28">
         <v>15</v>
@@ -2961,7 +2961,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="P29">
-        <v>0.04986997364462011</v>
+        <v>0.04986997364462013</v>
       </c>
       <c r="Q29">
         <v>0.9027777777777779</v>
@@ -3038,7 +3038,7 @@
         <v>0.2627118644067797</v>
       </c>
       <c r="P30">
-        <v>0.285207493265239</v>
+        <v>0.2852074932652396</v>
       </c>
       <c r="Q30">
         <v>0.4175701530612245</v>
@@ -3135,7 +3135,7 @@
         <v>0.2322097378277154</v>
       </c>
       <c r="P31">
-        <v>0.1556265945531601</v>
+        <v>0.1556265945531604</v>
       </c>
       <c r="Q31">
         <v>0.7608506944444444</v>
@@ -3232,7 +3232,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="P32">
-        <v>0.1963072587097571</v>
+        <v>0.1963072587097573</v>
       </c>
       <c r="Q32">
         <v>0.34765625</v>
@@ -3329,7 +3329,7 @@
         <v>0.2966507177033493</v>
       </c>
       <c r="P33">
-        <v>0.606863376011733</v>
+        <v>0.6068633760117338</v>
       </c>
       <c r="Q33">
         <v>0.2340364583333334</v>
@@ -3426,7 +3426,7 @@
         <v>0.246031746031746</v>
       </c>
       <c r="P34">
-        <v>0.5270445030072252</v>
+        <v>0.5270445030072258</v>
       </c>
       <c r="Q34">
         <v>0.4721237244897959</v>
@@ -3594,7 +3594,7 @@
         <v>0.2767857142857143</v>
       </c>
       <c r="P36">
-        <v>0.05545829422091494</v>
+        <v>0.05545829422091501</v>
       </c>
       <c r="Q36">
         <v>0.686530612244898</v>
@@ -3691,7 +3691,7 @@
         <v>0.1839762611275964</v>
       </c>
       <c r="P37">
-        <v>0.001236945685588573</v>
+        <v>0.001236945685588507</v>
       </c>
       <c r="Q37">
         <v>0.5</v>
@@ -3721,7 +3721,7 @@
         <v>22</v>
       </c>
       <c r="Z37">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AA37">
         <v>1</v>
@@ -3788,7 +3788,7 @@
         <v>0.2910798122065728</v>
       </c>
       <c r="P38">
-        <v>0.06812048270106598</v>
+        <v>0.06812048270106602</v>
       </c>
       <c r="Q38">
         <v>0.4414448979591837</v>
@@ -3885,7 +3885,7 @@
         <v>0.2431372549019608</v>
       </c>
       <c r="P39">
-        <v>0.01089577315301352</v>
+        <v>0.0108957731530135</v>
       </c>
       <c r="Q39">
         <v>1</v>
@@ -3915,7 +3915,7 @@
         <v>39</v>
       </c>
       <c r="Z39">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AA39">
         <v>1</v>
@@ -3982,7 +3982,7 @@
         <v>0.2393822393822394</v>
       </c>
       <c r="P40">
-        <v>0.438214443732844</v>
+        <v>0.4382144437328445</v>
       </c>
       <c r="Q40">
         <v>0.5292881944444444</v>
@@ -4079,7 +4079,7 @@
         <v>0.2393822393822394</v>
       </c>
       <c r="P41">
-        <v>0.438214443732844</v>
+        <v>0.4382144437328445</v>
       </c>
       <c r="Q41">
         <v>0.5292881944444444</v>
@@ -4173,7 +4173,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="P42">
-        <v>0.02413727288602275</v>
+        <v>0.02413727288602271</v>
       </c>
       <c r="Q42">
         <v>0.7402469135802467</v>
@@ -4203,7 +4203,7 @@
         <v>31</v>
       </c>
       <c r="Z42">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AA42">
         <v>15</v>
@@ -4270,7 +4270,7 @@
         <v>0.2672413793103448</v>
       </c>
       <c r="P43">
-        <v>0.04165861565409008</v>
+        <v>0.04165861565409009</v>
       </c>
       <c r="Q43">
         <v>1</v>
@@ -4367,7 +4367,7 @@
         <v>0.256198347107438</v>
       </c>
       <c r="P44">
-        <v>0.01871153087579451</v>
+        <v>0.01871153087579433</v>
       </c>
       <c r="Q44">
         <v>0.2601133786848072</v>
@@ -4397,7 +4397,7 @@
         <v>6</v>
       </c>
       <c r="Z44">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AA44">
         <v>4</v>
@@ -4458,7 +4458,7 @@
         <v>0.2046204620462046</v>
       </c>
       <c r="P45">
-        <v>0.003790535553194823</v>
+        <v>0.003790535553194845</v>
       </c>
       <c r="Q45">
         <v>1</v>
@@ -4488,7 +4488,7 @@
         <v>39</v>
       </c>
       <c r="Z45">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AA45">
         <v>1</v>
@@ -4555,7 +4555,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="P46">
-        <v>0.2279984327127861</v>
+        <v>0.2279984327127862</v>
       </c>
       <c r="Q46">
         <v>0.70703125</v>
@@ -4652,7 +4652,7 @@
         <v>0.2066666666666667</v>
       </c>
       <c r="P47">
-        <v>0.005298875417603694</v>
+        <v>0.005298875417603616</v>
       </c>
       <c r="Q47">
         <v>0.6949483497102544</v>
@@ -4682,7 +4682,7 @@
         <v>29</v>
       </c>
       <c r="Z47">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AA47">
         <v>14</v>
@@ -4749,7 +4749,7 @@
         <v>0.2066666666666667</v>
       </c>
       <c r="P48">
-        <v>0.005298875417603713</v>
+        <v>0.005298875417603649</v>
       </c>
       <c r="Q48">
         <v>0.6949483497102544</v>
@@ -4779,7 +4779,7 @@
         <v>29</v>
       </c>
       <c r="Z48">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AA48">
         <v>14</v>
@@ -4817,7 +4817,7 @@
         <v>0.161038961038961</v>
       </c>
       <c r="P49">
-        <v>0.006905590848685188</v>
+        <v>0.006905590848685194</v>
       </c>
       <c r="Q49">
         <v>1</v>
@@ -4847,7 +4847,7 @@
         <v>39</v>
       </c>
       <c r="Z49">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AA49">
         <v>1</v>
@@ -4914,7 +4914,7 @@
         <v>0.191358024691358</v>
       </c>
       <c r="P50">
-        <v>0.03408863327290811</v>
+        <v>0.03408863327290815</v>
       </c>
       <c r="Q50">
         <v>0.5</v>
@@ -5011,7 +5011,7 @@
         <v>0.1722222222222222</v>
       </c>
       <c r="P51">
-        <v>0.0021468661004493</v>
+        <v>0.00214686610044922</v>
       </c>
       <c r="Q51">
         <v>0.8888888888888888</v>
@@ -5041,7 +5041,7 @@
         <v>35</v>
       </c>
       <c r="Z51">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AA51">
         <v>15</v>
@@ -5088,7 +5088,7 @@
         <v>0.2330827067669173</v>
       </c>
       <c r="P52">
-        <v>0.08230408821726883</v>
+        <v>0.08230408821726891</v>
       </c>
       <c r="Q52">
         <v>0.78125</v>
@@ -5185,7 +5185,7 @@
         <v>0.1557788944723618</v>
       </c>
       <c r="P53">
-        <v>0.0002505773915408956</v>
+        <v>0.0002505773915408761</v>
       </c>
       <c r="Q53">
         <v>1</v>
@@ -5215,7 +5215,7 @@
         <v>39</v>
       </c>
       <c r="Z53">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AA53">
         <v>1</v>
@@ -5262,7 +5262,7 @@
         <v>0.2818181818181818</v>
       </c>
       <c r="P54">
-        <v>0.1210769133230427</v>
+        <v>0.1210769133230428</v>
       </c>
       <c r="Q54">
         <v>0.36328125</v>
@@ -5359,7 +5359,7 @@
         <v>0.1993569131832797</v>
       </c>
       <c r="P55">
-        <v>0.005447925395850126</v>
+        <v>0.005447925395850118</v>
       </c>
       <c r="Q55">
         <v>1</v>
@@ -5389,7 +5389,7 @@
         <v>39</v>
       </c>
       <c r="Z55">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AA55">
         <v>1</v>
@@ -5456,7 +5456,7 @@
         <v>0.3444444444444444</v>
       </c>
       <c r="P56">
-        <v>0.5730798804738924</v>
+        <v>0.5730798804738931</v>
       </c>
       <c r="Q56">
         <v>0.2646517148526077</v>
@@ -5550,7 +5550,7 @@
         <v>0.2583333333333334</v>
       </c>
       <c r="P57">
-        <v>0.1455854394958986</v>
+        <v>0.1455854394958987</v>
       </c>
       <c r="Q57">
         <v>0.9027777777777779</v>
@@ -5644,7 +5644,7 @@
         <v>0.2339622641509434</v>
       </c>
       <c r="P58">
-        <v>0.1613689194542328</v>
+        <v>0.161368919454233</v>
       </c>
       <c r="Q58">
         <v>0.5017361111111112</v>
@@ -5741,7 +5741,7 @@
         <v>0.2672413793103448</v>
       </c>
       <c r="P59">
-        <v>0.1969762873652419</v>
+        <v>0.1969762873652421</v>
       </c>
       <c r="Q59">
         <v>0.3472222222222222</v>
@@ -5935,7 +5935,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="P61">
-        <v>0.04986997364462012</v>
+        <v>0.04986997364462015</v>
       </c>
       <c r="Q61">
         <v>0.9027777777777779</v>
@@ -5965,7 +5965,7 @@
         <v>37</v>
       </c>
       <c r="Z61">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AA61">
         <v>15</v>
@@ -6032,7 +6032,7 @@
         <v>0.2206405693950178</v>
       </c>
       <c r="P62">
-        <v>0.02452746104359529</v>
+        <v>0.0245274610435953</v>
       </c>
       <c r="Q62">
         <v>1</v>
@@ -6129,7 +6129,7 @@
         <v>0.2384615384615385</v>
       </c>
       <c r="P63">
-        <v>0.3552799123856282</v>
+        <v>0.3552799123856284</v>
       </c>
       <c r="Q63">
         <v>0.6091666666666665</v>
@@ -6226,7 +6226,7 @@
         <v>0.2938388625592417</v>
       </c>
       <c r="P64">
-        <v>0.7252640270422734</v>
+        <v>0.7252640270422742</v>
       </c>
       <c r="Q64">
         <v>0.2385430839002267</v>

--- a/output/pharma_nordic_example_nodes.xlsx
+++ b/output/pharma_nordic_example_nodes.xlsx
@@ -532,7 +532,7 @@
         <v>0.2339622641509434</v>
       </c>
       <c r="P2">
-        <v>0.1627043167340306</v>
+        <v>0.1627043167340305</v>
       </c>
       <c r="Q2">
         <v>0.6566840277777779</v>
@@ -609,7 +609,7 @@
         <v>0.223826714801444</v>
       </c>
       <c r="P3">
-        <v>0.1979348761526409</v>
+        <v>0.1979348761526411</v>
       </c>
       <c r="Q3">
         <v>0.4583333333333333</v>
@@ -686,7 +686,7 @@
         <v>0.3625730994152047</v>
       </c>
       <c r="P4">
-        <v>0.2056428338727418</v>
+        <v>0.2056428338727423</v>
       </c>
       <c r="Q4">
         <v>0.1773469387755102</v>
@@ -780,7 +780,7 @@
         <v>0.2123287671232877</v>
       </c>
       <c r="P5">
-        <v>0.003154190793945012</v>
+        <v>0.003154190793945104</v>
       </c>
       <c r="Q5">
         <v>1</v>
@@ -810,7 +810,7 @@
         <v>39</v>
       </c>
       <c r="Z5">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AA5">
         <v>1</v>
@@ -877,7 +877,7 @@
         <v>0.2683982683982684</v>
       </c>
       <c r="P6">
-        <v>0.0155702901610576</v>
+        <v>0.01557029016105825</v>
       </c>
       <c r="Q6">
         <v>0.2401</v>
@@ -907,7 +907,7 @@
         <v>5</v>
       </c>
       <c r="Z6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA6">
         <v>3</v>
@@ -974,7 +974,7 @@
         <v>0.223021582733813</v>
       </c>
       <c r="P7">
-        <v>0.005855458830191469</v>
+        <v>0.005855458830191972</v>
       </c>
       <c r="Q7">
         <v>0.305</v>
@@ -1004,7 +1004,7 @@
         <v>9</v>
       </c>
       <c r="Z7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AA7">
         <v>5</v>
@@ -1071,7 +1071,7 @@
         <v>0.1828908554572271</v>
       </c>
       <c r="P8">
-        <v>0.001186184338600607</v>
+        <v>0.001186184338600728</v>
       </c>
       <c r="Q8">
         <v>1</v>
@@ -1101,7 +1101,7 @@
         <v>39</v>
       </c>
       <c r="Z8">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AA8">
         <v>1</v>
@@ -1168,7 +1168,7 @@
         <v>0.2052980132450331</v>
       </c>
       <c r="P9">
-        <v>0.004753484704332955</v>
+        <v>0.004753484704333141</v>
       </c>
       <c r="Q9">
         <v>0.8890306122448979</v>
@@ -1198,7 +1198,7 @@
         <v>36</v>
       </c>
       <c r="Z9">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AA9">
         <v>15</v>
@@ -1265,7 +1265,7 @@
         <v>0.2052980132450331</v>
       </c>
       <c r="P10">
-        <v>0.00475348470433297</v>
+        <v>0.00475348470433317</v>
       </c>
       <c r="Q10">
         <v>0.8890306122448979</v>
@@ -1295,7 +1295,7 @@
         <v>36</v>
       </c>
       <c r="Z10">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AA10">
         <v>15</v>
@@ -1362,7 +1362,7 @@
         <v>0.1861861861861862</v>
       </c>
       <c r="P11">
-        <v>0.002771926326836659</v>
+        <v>0.002771926326836912</v>
       </c>
       <c r="Q11">
         <v>0.9225</v>
@@ -1392,7 +1392,7 @@
         <v>38</v>
       </c>
       <c r="Z11">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AA11">
         <v>15</v>
@@ -1527,7 +1527,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="P13">
-        <v>0.02413727288602273</v>
+        <v>0.02413727288602298</v>
       </c>
       <c r="Q13">
         <v>0.7402469135802467</v>
@@ -1557,7 +1557,7 @@
         <v>31</v>
       </c>
       <c r="Z13">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AA13">
         <v>15</v>
@@ -1701,7 +1701,7 @@
         <v>0.2271062271062271</v>
       </c>
       <c r="P15">
-        <v>0.01091136045999138</v>
+        <v>0.01091136045999195</v>
       </c>
       <c r="Q15">
         <v>0.3401000000000001</v>
@@ -1731,7 +1731,7 @@
         <v>10</v>
       </c>
       <c r="Z15">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AA15">
         <v>7</v>
@@ -1798,7 +1798,7 @@
         <v>0.2583333333333334</v>
       </c>
       <c r="P16">
-        <v>0.1455854394958986</v>
+        <v>0.1455854394958988</v>
       </c>
       <c r="Q16">
         <v>0.9027777777777779</v>
@@ -1828,7 +1828,7 @@
         <v>37</v>
       </c>
       <c r="Z16">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA16">
         <v>15</v>
@@ -1875,7 +1875,7 @@
         <v>0.256198347107438</v>
       </c>
       <c r="P17">
-        <v>0.5186239472089471</v>
+        <v>0.5186239472089472</v>
       </c>
       <c r="Q17">
         <v>0.4151929209183673</v>
@@ -1966,7 +1966,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="P18">
-        <v>0.04986997364462014</v>
+        <v>0.04986997364462034</v>
       </c>
       <c r="Q18">
         <v>0.9027777777777779</v>
@@ -1996,7 +1996,7 @@
         <v>37</v>
       </c>
       <c r="Z18">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AA18">
         <v>15</v>
@@ -2063,7 +2063,7 @@
         <v>0.2145328719723184</v>
       </c>
       <c r="P19">
-        <v>0.04448123221594937</v>
+        <v>0.04448123221594971</v>
       </c>
       <c r="Q19">
         <v>0.6111111111111112</v>
@@ -2093,7 +2093,7 @@
         <v>26</v>
       </c>
       <c r="Z19">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AA19">
         <v>11</v>
@@ -2140,7 +2140,7 @@
         <v>0.3195876288659794</v>
       </c>
       <c r="P20">
-        <v>0.05378569674578799</v>
+        <v>0.05378569674578844</v>
       </c>
       <c r="Q20">
         <v>0.2622448979591837</v>
@@ -2237,7 +2237,7 @@
         <v>0.2897196261682243</v>
       </c>
       <c r="P21">
-        <v>0.1019516679235185</v>
+        <v>0.1019516679235187</v>
       </c>
       <c r="Q21">
         <v>0.4822530864197531</v>
@@ -2331,7 +2331,7 @@
         <v>0.248</v>
       </c>
       <c r="P22">
-        <v>0.02689303999999563</v>
+        <v>0.02689303999999619</v>
       </c>
       <c r="Q22">
         <v>0.3792</v>
@@ -2361,7 +2361,7 @@
         <v>14</v>
       </c>
       <c r="Z22">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AA22">
         <v>10</v>
@@ -2408,7 +2408,7 @@
         <v>0.1861861861861862</v>
       </c>
       <c r="P23">
-        <v>0.002771926326836658</v>
+        <v>0.002771926326836911</v>
       </c>
       <c r="Q23">
         <v>0.9225</v>
@@ -2438,7 +2438,7 @@
         <v>38</v>
       </c>
       <c r="Z23">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AA23">
         <v>15</v>
@@ -2505,7 +2505,7 @@
         <v>0.2123287671232877</v>
       </c>
       <c r="P24">
-        <v>0.003154190793944997</v>
+        <v>0.003154190793945123</v>
       </c>
       <c r="Q24">
         <v>1</v>
@@ -2676,7 +2676,7 @@
         <v>0.25</v>
       </c>
       <c r="P26">
-        <v>0.01468630870620831</v>
+        <v>0.01468630870620846</v>
       </c>
       <c r="Q26">
         <v>0.686530612244898</v>
@@ -2706,7 +2706,7 @@
         <v>28</v>
       </c>
       <c r="Z26">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AA26">
         <v>15</v>
@@ -2773,7 +2773,7 @@
         <v>0.1776504297994269</v>
       </c>
       <c r="P27">
-        <v>0.01130002982502724</v>
+        <v>0.01130002982502749</v>
       </c>
       <c r="Q27">
         <v>1.006944444444444</v>
@@ -2803,7 +2803,7 @@
         <v>40</v>
       </c>
       <c r="Z27">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AA27">
         <v>15</v>
@@ -2867,7 +2867,7 @@
         <v>0.1776504297994269</v>
       </c>
       <c r="P28">
-        <v>0.01130002982502725</v>
+        <v>0.01130002982502751</v>
       </c>
       <c r="Q28">
         <v>1.006944444444444</v>
@@ -2897,7 +2897,7 @@
         <v>40</v>
       </c>
       <c r="Z28">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AA28">
         <v>15</v>
@@ -2961,7 +2961,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="P29">
-        <v>0.04986997364462013</v>
+        <v>0.04986997364462031</v>
       </c>
       <c r="Q29">
         <v>0.9027777777777779</v>
@@ -3038,7 +3038,7 @@
         <v>0.2627118644067797</v>
       </c>
       <c r="P30">
-        <v>0.2852074932652396</v>
+        <v>0.2852074932652397</v>
       </c>
       <c r="Q30">
         <v>0.4175701530612245</v>
@@ -3135,7 +3135,7 @@
         <v>0.2322097378277154</v>
       </c>
       <c r="P31">
-        <v>0.1556265945531604</v>
+        <v>0.1556265945531603</v>
       </c>
       <c r="Q31">
         <v>0.7608506944444444</v>
@@ -3232,7 +3232,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="P32">
-        <v>0.1963072587097573</v>
+        <v>0.1963072587097578</v>
       </c>
       <c r="Q32">
         <v>0.34765625</v>
@@ -3329,7 +3329,7 @@
         <v>0.2966507177033493</v>
       </c>
       <c r="P33">
-        <v>0.6068633760117338</v>
+        <v>0.6068633760117343</v>
       </c>
       <c r="Q33">
         <v>0.2340364583333334</v>
@@ -3426,7 +3426,7 @@
         <v>0.246031746031746</v>
       </c>
       <c r="P34">
-        <v>0.5270445030072258</v>
+        <v>0.5270445030072261</v>
       </c>
       <c r="Q34">
         <v>0.4721237244897959</v>
@@ -3523,7 +3523,7 @@
         <v>0.2421875</v>
       </c>
       <c r="P35">
-        <v>0.1006532410491348</v>
+        <v>0.1006532410491352</v>
       </c>
       <c r="Q35">
         <v>0.4822530864197531</v>
@@ -3594,7 +3594,7 @@
         <v>0.2767857142857143</v>
       </c>
       <c r="P36">
-        <v>0.05545829422091501</v>
+        <v>0.05545829422091517</v>
       </c>
       <c r="Q36">
         <v>0.686530612244898</v>
@@ -3691,7 +3691,7 @@
         <v>0.1839762611275964</v>
       </c>
       <c r="P37">
-        <v>0.001236945685588507</v>
+        <v>0.001236945685588771</v>
       </c>
       <c r="Q37">
         <v>0.5</v>
@@ -3721,7 +3721,7 @@
         <v>22</v>
       </c>
       <c r="Z37">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AA37">
         <v>1</v>
@@ -3788,7 +3788,7 @@
         <v>0.2910798122065728</v>
       </c>
       <c r="P38">
-        <v>0.06812048270106602</v>
+        <v>0.06812048270106651</v>
       </c>
       <c r="Q38">
         <v>0.4414448979591837</v>
@@ -3885,7 +3885,7 @@
         <v>0.2431372549019608</v>
       </c>
       <c r="P39">
-        <v>0.0108957731530135</v>
+        <v>0.01089577315301358</v>
       </c>
       <c r="Q39">
         <v>1</v>
@@ -3915,7 +3915,7 @@
         <v>39</v>
       </c>
       <c r="Z39">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AA39">
         <v>1</v>
@@ -3982,7 +3982,7 @@
         <v>0.2393822393822394</v>
       </c>
       <c r="P40">
-        <v>0.4382144437328445</v>
+        <v>0.4382144437328448</v>
       </c>
       <c r="Q40">
         <v>0.5292881944444444</v>
@@ -4012,7 +4012,7 @@
         <v>24</v>
       </c>
       <c r="Z40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA40">
         <v>14</v>
@@ -4079,7 +4079,7 @@
         <v>0.2393822393822394</v>
       </c>
       <c r="P41">
-        <v>0.4382144437328445</v>
+        <v>0.4382144437328448</v>
       </c>
       <c r="Q41">
         <v>0.5292881944444444</v>
@@ -4109,7 +4109,7 @@
         <v>24</v>
       </c>
       <c r="Z41">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA41">
         <v>14</v>
@@ -4173,7 +4173,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="P42">
-        <v>0.02413727288602271</v>
+        <v>0.02413727288602304</v>
       </c>
       <c r="Q42">
         <v>0.7402469135802467</v>
@@ -4270,7 +4270,7 @@
         <v>0.2672413793103448</v>
       </c>
       <c r="P43">
-        <v>0.04165861565409009</v>
+        <v>0.04165861565409019</v>
       </c>
       <c r="Q43">
         <v>1</v>
@@ -4300,7 +4300,7 @@
         <v>39</v>
       </c>
       <c r="Z43">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AA43">
         <v>1</v>
@@ -4367,7 +4367,7 @@
         <v>0.256198347107438</v>
       </c>
       <c r="P44">
-        <v>0.01871153087579433</v>
+        <v>0.01871153087579515</v>
       </c>
       <c r="Q44">
         <v>0.2601133786848072</v>
@@ -4397,7 +4397,7 @@
         <v>6</v>
       </c>
       <c r="Z44">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AA44">
         <v>4</v>
@@ -4458,7 +4458,7 @@
         <v>0.2046204620462046</v>
       </c>
       <c r="P45">
-        <v>0.003790535553194845</v>
+        <v>0.003790535553194937</v>
       </c>
       <c r="Q45">
         <v>1</v>
@@ -4488,7 +4488,7 @@
         <v>39</v>
       </c>
       <c r="Z45">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AA45">
         <v>1</v>
@@ -4555,7 +4555,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="P46">
-        <v>0.2279984327127862</v>
+        <v>0.2279984327127863</v>
       </c>
       <c r="Q46">
         <v>0.70703125</v>
@@ -4652,7 +4652,7 @@
         <v>0.2066666666666667</v>
       </c>
       <c r="P47">
-        <v>0.005298875417603616</v>
+        <v>0.005298875417603955</v>
       </c>
       <c r="Q47">
         <v>0.6949483497102544</v>
@@ -4682,7 +4682,7 @@
         <v>29</v>
       </c>
       <c r="Z47">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AA47">
         <v>14</v>
@@ -4749,7 +4749,7 @@
         <v>0.2066666666666667</v>
       </c>
       <c r="P48">
-        <v>0.005298875417603649</v>
+        <v>0.005298875417603974</v>
       </c>
       <c r="Q48">
         <v>0.6949483497102544</v>
@@ -4779,7 +4779,7 @@
         <v>29</v>
       </c>
       <c r="Z48">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AA48">
         <v>14</v>
@@ -4817,7 +4817,7 @@
         <v>0.161038961038961</v>
       </c>
       <c r="P49">
-        <v>0.006905590848685194</v>
+        <v>0.006905590848685319</v>
       </c>
       <c r="Q49">
         <v>1</v>
@@ -4847,7 +4847,7 @@
         <v>39</v>
       </c>
       <c r="Z49">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AA49">
         <v>1</v>
@@ -4914,7 +4914,7 @@
         <v>0.191358024691358</v>
       </c>
       <c r="P50">
-        <v>0.03408863327290815</v>
+        <v>0.03408863327290836</v>
       </c>
       <c r="Q50">
         <v>0.5</v>
@@ -4944,7 +4944,7 @@
         <v>22</v>
       </c>
       <c r="Z50">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AA50">
         <v>1</v>
@@ -5011,7 +5011,7 @@
         <v>0.1722222222222222</v>
       </c>
       <c r="P51">
-        <v>0.00214686610044922</v>
+        <v>0.002146866100449477</v>
       </c>
       <c r="Q51">
         <v>0.8888888888888888</v>
@@ -5041,7 +5041,7 @@
         <v>35</v>
       </c>
       <c r="Z51">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AA51">
         <v>15</v>
@@ -5088,7 +5088,7 @@
         <v>0.2330827067669173</v>
       </c>
       <c r="P52">
-        <v>0.08230408821726891</v>
+        <v>0.08230408821726912</v>
       </c>
       <c r="Q52">
         <v>0.78125</v>
@@ -5185,7 +5185,7 @@
         <v>0.1557788944723618</v>
       </c>
       <c r="P53">
-        <v>0.0002505773915408761</v>
+        <v>0.0002505773915410015</v>
       </c>
       <c r="Q53">
         <v>1</v>
@@ -5215,7 +5215,7 @@
         <v>39</v>
       </c>
       <c r="Z53">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AA53">
         <v>1</v>
@@ -5262,7 +5262,7 @@
         <v>0.2818181818181818</v>
       </c>
       <c r="P54">
-        <v>0.1210769133230428</v>
+        <v>0.1210769133230431</v>
       </c>
       <c r="Q54">
         <v>0.36328125</v>
@@ -5359,7 +5359,7 @@
         <v>0.1993569131832797</v>
       </c>
       <c r="P55">
-        <v>0.005447925395850118</v>
+        <v>0.005447925395850194</v>
       </c>
       <c r="Q55">
         <v>1</v>
@@ -5389,7 +5389,7 @@
         <v>39</v>
       </c>
       <c r="Z55">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AA55">
         <v>1</v>
@@ -5456,7 +5456,7 @@
         <v>0.3444444444444444</v>
       </c>
       <c r="P56">
-        <v>0.5730798804738931</v>
+        <v>0.573079880473893</v>
       </c>
       <c r="Q56">
         <v>0.2646517148526077</v>
@@ -5550,7 +5550,7 @@
         <v>0.2583333333333334</v>
       </c>
       <c r="P57">
-        <v>0.1455854394958987</v>
+        <v>0.1455854394958988</v>
       </c>
       <c r="Q57">
         <v>0.9027777777777779</v>
@@ -5580,7 +5580,7 @@
         <v>37</v>
       </c>
       <c r="Z57">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA57">
         <v>15</v>
@@ -5644,7 +5644,7 @@
         <v>0.2339622641509434</v>
       </c>
       <c r="P58">
-        <v>0.161368919454233</v>
+        <v>0.1613689194542332</v>
       </c>
       <c r="Q58">
         <v>0.5017361111111112</v>
@@ -5741,7 +5741,7 @@
         <v>0.2672413793103448</v>
       </c>
       <c r="P59">
-        <v>0.1969762873652421</v>
+        <v>0.1969762873652424</v>
       </c>
       <c r="Q59">
         <v>0.3472222222222222</v>
@@ -5838,7 +5838,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="P60">
-        <v>0.04986997364462015</v>
+        <v>0.04986997364462029</v>
       </c>
       <c r="Q60">
         <v>0.9027777777777779</v>
@@ -5868,7 +5868,7 @@
         <v>37</v>
       </c>
       <c r="Z60">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="AA60">
         <v>15</v>
@@ -5935,7 +5935,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="P61">
-        <v>0.04986997364462015</v>
+        <v>0.04986997364462032</v>
       </c>
       <c r="Q61">
         <v>0.9027777777777779</v>
@@ -5965,7 +5965,7 @@
         <v>37</v>
       </c>
       <c r="Z61">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AA61">
         <v>15</v>
@@ -6032,7 +6032,7 @@
         <v>0.2206405693950178</v>
       </c>
       <c r="P62">
-        <v>0.0245274610435953</v>
+        <v>0.0245274610435954</v>
       </c>
       <c r="Q62">
         <v>1</v>
@@ -6062,7 +6062,7 @@
         <v>39</v>
       </c>
       <c r="Z62">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AA62">
         <v>1</v>

--- a/output/pharma_nordic_example_nodes.xlsx
+++ b/output/pharma_nordic_example_nodes.xlsx
@@ -532,7 +532,7 @@
         <v>0.2339622641509434</v>
       </c>
       <c r="P2">
-        <v>0.1627043167340305</v>
+        <v>0.1627043167340304</v>
       </c>
       <c r="Q2">
         <v>0.6566840277777779</v>
@@ -609,7 +609,7 @@
         <v>0.223826714801444</v>
       </c>
       <c r="P3">
-        <v>0.1979348761526411</v>
+        <v>0.1979348761526408</v>
       </c>
       <c r="Q3">
         <v>0.4583333333333333</v>
@@ -686,7 +686,7 @@
         <v>0.3625730994152047</v>
       </c>
       <c r="P4">
-        <v>0.2056428338727423</v>
+        <v>0.2056428338727412</v>
       </c>
       <c r="Q4">
         <v>0.1773469387755102</v>
@@ -780,7 +780,7 @@
         <v>0.2123287671232877</v>
       </c>
       <c r="P5">
-        <v>0.003154190793945104</v>
+        <v>0.003154190793945037</v>
       </c>
       <c r="Q5">
         <v>1</v>
@@ -810,7 +810,7 @@
         <v>39</v>
       </c>
       <c r="Z5">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="AA5">
         <v>1</v>
@@ -877,7 +877,7 @@
         <v>0.2683982683982684</v>
       </c>
       <c r="P6">
-        <v>0.01557029016105825</v>
+        <v>0.01557029016105773</v>
       </c>
       <c r="Q6">
         <v>0.2401</v>
@@ -907,7 +907,7 @@
         <v>5</v>
       </c>
       <c r="Z6">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AA6">
         <v>3</v>
@@ -974,7 +974,7 @@
         <v>0.223021582733813</v>
       </c>
       <c r="P7">
-        <v>0.005855458830191972</v>
+        <v>0.005855458830191629</v>
       </c>
       <c r="Q7">
         <v>0.305</v>
@@ -1004,7 +1004,7 @@
         <v>9</v>
       </c>
       <c r="Z7">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AA7">
         <v>5</v>
@@ -1071,7 +1071,7 @@
         <v>0.1828908554572271</v>
       </c>
       <c r="P8">
-        <v>0.001186184338600728</v>
+        <v>0.001186184338600645</v>
       </c>
       <c r="Q8">
         <v>1</v>
@@ -1101,7 +1101,7 @@
         <v>39</v>
       </c>
       <c r="Z8">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AA8">
         <v>1</v>
@@ -1168,7 +1168,7 @@
         <v>0.2052980132450331</v>
       </c>
       <c r="P9">
-        <v>0.004753484704333141</v>
+        <v>0.004753484704332994</v>
       </c>
       <c r="Q9">
         <v>0.8890306122448979</v>
@@ -1198,7 +1198,7 @@
         <v>36</v>
       </c>
       <c r="Z9">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AA9">
         <v>15</v>
@@ -1265,7 +1265,7 @@
         <v>0.2052980132450331</v>
       </c>
       <c r="P10">
-        <v>0.00475348470433317</v>
+        <v>0.004753484704333005</v>
       </c>
       <c r="Q10">
         <v>0.8890306122448979</v>
@@ -1295,7 +1295,7 @@
         <v>36</v>
       </c>
       <c r="Z10">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AA10">
         <v>15</v>
@@ -1362,7 +1362,7 @@
         <v>0.1861861861861862</v>
       </c>
       <c r="P11">
-        <v>0.002771926326836912</v>
+        <v>0.002771926326836728</v>
       </c>
       <c r="Q11">
         <v>0.9225</v>
@@ -1439,7 +1439,7 @@
         <v>0.248</v>
       </c>
       <c r="P12">
-        <v>0.4792480623402848</v>
+        <v>0.4792480623402846</v>
       </c>
       <c r="Q12">
         <v>0.4073600481859411</v>
@@ -1527,7 +1527,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="P13">
-        <v>0.02413727288602298</v>
+        <v>0.02413727288602261</v>
       </c>
       <c r="Q13">
         <v>0.7402469135802467</v>
@@ -1557,7 +1557,7 @@
         <v>31</v>
       </c>
       <c r="Z13">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA13">
         <v>15</v>
@@ -1624,7 +1624,7 @@
         <v>0.2339622641509434</v>
       </c>
       <c r="P14">
-        <v>0.2745492459451345</v>
+        <v>0.2745492459451341</v>
       </c>
       <c r="Q14">
         <v>0.7469444444444444</v>
@@ -1701,7 +1701,7 @@
         <v>0.2271062271062271</v>
       </c>
       <c r="P15">
-        <v>0.01091136045999195</v>
+        <v>0.01091136045999159</v>
       </c>
       <c r="Q15">
         <v>0.3401000000000001</v>
@@ -1731,7 +1731,7 @@
         <v>10</v>
       </c>
       <c r="Z15">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AA15">
         <v>7</v>
@@ -1798,7 +1798,7 @@
         <v>0.2583333333333334</v>
       </c>
       <c r="P16">
-        <v>0.1455854394958988</v>
+        <v>0.1455854394958986</v>
       </c>
       <c r="Q16">
         <v>0.9027777777777779</v>
@@ -1875,7 +1875,7 @@
         <v>0.256198347107438</v>
       </c>
       <c r="P17">
-        <v>0.5186239472089472</v>
+        <v>0.5186239472089464</v>
       </c>
       <c r="Q17">
         <v>0.4151929209183673</v>
@@ -1966,7 +1966,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="P18">
-        <v>0.04986997364462034</v>
+        <v>0.04986997364462023</v>
       </c>
       <c r="Q18">
         <v>0.9027777777777779</v>
@@ -1996,7 +1996,7 @@
         <v>37</v>
       </c>
       <c r="Z18">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AA18">
         <v>15</v>
@@ -2063,7 +2063,7 @@
         <v>0.2145328719723184</v>
       </c>
       <c r="P19">
-        <v>0.04448123221594971</v>
+        <v>0.04448123221594951</v>
       </c>
       <c r="Q19">
         <v>0.6111111111111112</v>
@@ -2093,7 +2093,7 @@
         <v>26</v>
       </c>
       <c r="Z19">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AA19">
         <v>11</v>
@@ -2140,7 +2140,7 @@
         <v>0.3195876288659794</v>
       </c>
       <c r="P20">
-        <v>0.05378569674578844</v>
+        <v>0.05378569674578802</v>
       </c>
       <c r="Q20">
         <v>0.2622448979591837</v>
@@ -2237,7 +2237,7 @@
         <v>0.2897196261682243</v>
       </c>
       <c r="P21">
-        <v>0.1019516679235187</v>
+        <v>0.1019516679235184</v>
       </c>
       <c r="Q21">
         <v>0.4822530864197531</v>
@@ -2331,7 +2331,7 @@
         <v>0.248</v>
       </c>
       <c r="P22">
-        <v>0.02689303999999619</v>
+        <v>0.02689303999999553</v>
       </c>
       <c r="Q22">
         <v>0.3792</v>
@@ -2361,7 +2361,7 @@
         <v>14</v>
       </c>
       <c r="Z22">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AA22">
         <v>10</v>
@@ -2408,7 +2408,7 @@
         <v>0.1861861861861862</v>
       </c>
       <c r="P23">
-        <v>0.002771926326836911</v>
+        <v>0.002771926326836765</v>
       </c>
       <c r="Q23">
         <v>0.9225</v>
@@ -2438,7 +2438,7 @@
         <v>38</v>
       </c>
       <c r="Z23">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="AA23">
         <v>15</v>
@@ -2505,7 +2505,7 @@
         <v>0.2123287671232877</v>
       </c>
       <c r="P24">
-        <v>0.003154190793945123</v>
+        <v>0.003154190793945022</v>
       </c>
       <c r="Q24">
         <v>1</v>
@@ -2676,7 +2676,7 @@
         <v>0.25</v>
       </c>
       <c r="P26">
-        <v>0.01468630870620846</v>
+        <v>0.01468630870620827</v>
       </c>
       <c r="Q26">
         <v>0.686530612244898</v>
@@ -2706,7 +2706,7 @@
         <v>28</v>
       </c>
       <c r="Z26">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AA26">
         <v>15</v>
@@ -2773,7 +2773,7 @@
         <v>0.1776504297994269</v>
       </c>
       <c r="P27">
-        <v>0.01130002982502749</v>
+        <v>0.01130002982502741</v>
       </c>
       <c r="Q27">
         <v>1.006944444444444</v>
@@ -2803,7 +2803,7 @@
         <v>40</v>
       </c>
       <c r="Z27">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AA27">
         <v>15</v>
@@ -2867,7 +2867,7 @@
         <v>0.1776504297994269</v>
       </c>
       <c r="P28">
-        <v>0.01130002982502751</v>
+        <v>0.01130002982502742</v>
       </c>
       <c r="Q28">
         <v>1.006944444444444</v>
@@ -2897,7 +2897,7 @@
         <v>40</v>
       </c>
       <c r="Z28">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AA28">
         <v>15</v>
@@ -2961,7 +2961,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="P29">
-        <v>0.04986997364462031</v>
+        <v>0.04986997364462024</v>
       </c>
       <c r="Q29">
         <v>0.9027777777777779</v>
@@ -2991,7 +2991,7 @@
         <v>37</v>
       </c>
       <c r="Z29">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA29">
         <v>15</v>
@@ -3038,7 +3038,7 @@
         <v>0.2627118644067797</v>
       </c>
       <c r="P30">
-        <v>0.2852074932652397</v>
+        <v>0.2852074932652394</v>
       </c>
       <c r="Q30">
         <v>0.4175701530612245</v>
@@ -3232,7 +3232,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="P32">
-        <v>0.1963072587097578</v>
+        <v>0.1963072587097575</v>
       </c>
       <c r="Q32">
         <v>0.34765625</v>
@@ -3329,7 +3329,7 @@
         <v>0.2966507177033493</v>
       </c>
       <c r="P33">
-        <v>0.6068633760117343</v>
+        <v>0.606863376011733</v>
       </c>
       <c r="Q33">
         <v>0.2340364583333334</v>
@@ -3426,7 +3426,7 @@
         <v>0.246031746031746</v>
       </c>
       <c r="P34">
-        <v>0.5270445030072261</v>
+        <v>0.5270445030072252</v>
       </c>
       <c r="Q34">
         <v>0.4721237244897959</v>
@@ -3523,7 +3523,7 @@
         <v>0.2421875</v>
       </c>
       <c r="P35">
-        <v>0.1006532410491352</v>
+        <v>0.1006532410491349</v>
       </c>
       <c r="Q35">
         <v>0.4822530864197531</v>
@@ -3594,7 +3594,7 @@
         <v>0.2767857142857143</v>
       </c>
       <c r="P36">
-        <v>0.05545829422091517</v>
+        <v>0.05545829422091474</v>
       </c>
       <c r="Q36">
         <v>0.686530612244898</v>
@@ -3691,7 +3691,7 @@
         <v>0.1839762611275964</v>
       </c>
       <c r="P37">
-        <v>0.001236945685588771</v>
+        <v>0.001236945685588622</v>
       </c>
       <c r="Q37">
         <v>0.5</v>
@@ -3721,7 +3721,7 @@
         <v>22</v>
       </c>
       <c r="Z37">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AA37">
         <v>1</v>
@@ -3788,7 +3788,7 @@
         <v>0.2910798122065728</v>
       </c>
       <c r="P38">
-        <v>0.06812048270106651</v>
+        <v>0.0681204827010658</v>
       </c>
       <c r="Q38">
         <v>0.4414448979591837</v>
@@ -3885,7 +3885,7 @@
         <v>0.2431372549019608</v>
       </c>
       <c r="P39">
-        <v>0.01089577315301358</v>
+        <v>0.01089577315301343</v>
       </c>
       <c r="Q39">
         <v>1</v>
@@ -3915,7 +3915,7 @@
         <v>39</v>
       </c>
       <c r="Z39">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AA39">
         <v>1</v>
@@ -3982,7 +3982,7 @@
         <v>0.2393822393822394</v>
       </c>
       <c r="P40">
-        <v>0.4382144437328448</v>
+        <v>0.4382144437328442</v>
       </c>
       <c r="Q40">
         <v>0.5292881944444444</v>
@@ -4079,7 +4079,7 @@
         <v>0.2393822393822394</v>
       </c>
       <c r="P41">
-        <v>0.4382144437328448</v>
+        <v>0.4382144437328443</v>
       </c>
       <c r="Q41">
         <v>0.5292881944444444</v>
@@ -4173,7 +4173,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="P42">
-        <v>0.02413727288602304</v>
+        <v>0.02413727288602257</v>
       </c>
       <c r="Q42">
         <v>0.7402469135802467</v>
@@ -4270,7 +4270,7 @@
         <v>0.2672413793103448</v>
       </c>
       <c r="P43">
-        <v>0.04165861565409019</v>
+        <v>0.04165861565409001</v>
       </c>
       <c r="Q43">
         <v>1</v>
@@ -4300,7 +4300,7 @@
         <v>39</v>
       </c>
       <c r="Z43">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA43">
         <v>1</v>
@@ -4367,7 +4367,7 @@
         <v>0.256198347107438</v>
       </c>
       <c r="P44">
-        <v>0.01871153087579515</v>
+        <v>0.01871153087579444</v>
       </c>
       <c r="Q44">
         <v>0.2601133786848072</v>
@@ -4397,7 +4397,7 @@
         <v>6</v>
       </c>
       <c r="Z44">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA44">
         <v>4</v>
@@ -4458,7 +4458,7 @@
         <v>0.2046204620462046</v>
       </c>
       <c r="P45">
-        <v>0.003790535553194937</v>
+        <v>0.003790535553194864</v>
       </c>
       <c r="Q45">
         <v>1</v>
@@ -4488,7 +4488,7 @@
         <v>39</v>
       </c>
       <c r="Z45">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AA45">
         <v>1</v>
@@ -4555,7 +4555,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="P46">
-        <v>0.2279984327127863</v>
+        <v>0.2279984327127859</v>
       </c>
       <c r="Q46">
         <v>0.70703125</v>
@@ -4652,7 +4652,7 @@
         <v>0.2066666666666667</v>
       </c>
       <c r="P47">
-        <v>0.005298875417603955</v>
+        <v>0.005298875417603717</v>
       </c>
       <c r="Q47">
         <v>0.6949483497102544</v>
@@ -4682,7 +4682,7 @@
         <v>29</v>
       </c>
       <c r="Z47">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="AA47">
         <v>14</v>
@@ -4749,7 +4749,7 @@
         <v>0.2066666666666667</v>
       </c>
       <c r="P48">
-        <v>0.005298875417603974</v>
+        <v>0.005298875417603682</v>
       </c>
       <c r="Q48">
         <v>0.6949483497102544</v>
@@ -4817,7 +4817,7 @@
         <v>0.161038961038961</v>
       </c>
       <c r="P49">
-        <v>0.006905590848685319</v>
+        <v>0.006905590848685274</v>
       </c>
       <c r="Q49">
         <v>1</v>
@@ -4847,7 +4847,7 @@
         <v>39</v>
       </c>
       <c r="Z49">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA49">
         <v>1</v>
@@ -4914,7 +4914,7 @@
         <v>0.191358024691358</v>
       </c>
       <c r="P50">
-        <v>0.03408863327290836</v>
+        <v>0.0340886332729082</v>
       </c>
       <c r="Q50">
         <v>0.5</v>
@@ -4944,7 +4944,7 @@
         <v>22</v>
       </c>
       <c r="Z50">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AA50">
         <v>1</v>
@@ -5011,7 +5011,7 @@
         <v>0.1722222222222222</v>
       </c>
       <c r="P51">
-        <v>0.002146866100449477</v>
+        <v>0.002146866100449281</v>
       </c>
       <c r="Q51">
         <v>0.8888888888888888</v>
@@ -5041,7 +5041,7 @@
         <v>35</v>
       </c>
       <c r="Z51">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AA51">
         <v>15</v>
@@ -5088,7 +5088,7 @@
         <v>0.2330827067669173</v>
       </c>
       <c r="P52">
-        <v>0.08230408821726912</v>
+        <v>0.08230408821726885</v>
       </c>
       <c r="Q52">
         <v>0.78125</v>
@@ -5185,7 +5185,7 @@
         <v>0.1557788944723618</v>
       </c>
       <c r="P53">
-        <v>0.0002505773915410015</v>
+        <v>0.000250577391540954</v>
       </c>
       <c r="Q53">
         <v>1</v>
@@ -5215,7 +5215,7 @@
         <v>39</v>
       </c>
       <c r="Z53">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AA53">
         <v>1</v>
@@ -5262,7 +5262,7 @@
         <v>0.2818181818181818</v>
       </c>
       <c r="P54">
-        <v>0.1210769133230431</v>
+        <v>0.1210769133230427</v>
       </c>
       <c r="Q54">
         <v>0.36328125</v>
@@ -5359,7 +5359,7 @@
         <v>0.1993569131832797</v>
       </c>
       <c r="P55">
-        <v>0.005447925395850194</v>
+        <v>0.00544792539585006</v>
       </c>
       <c r="Q55">
         <v>1</v>
@@ -5389,7 +5389,7 @@
         <v>39</v>
       </c>
       <c r="Z55">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA55">
         <v>1</v>
@@ -5456,7 +5456,7 @@
         <v>0.3444444444444444</v>
       </c>
       <c r="P56">
-        <v>0.573079880473893</v>
+        <v>0.5730798804738927</v>
       </c>
       <c r="Q56">
         <v>0.2646517148526077</v>
@@ -5550,7 +5550,7 @@
         <v>0.2583333333333334</v>
       </c>
       <c r="P57">
-        <v>0.1455854394958988</v>
+        <v>0.1455854394958985</v>
       </c>
       <c r="Q57">
         <v>0.9027777777777779</v>
@@ -5644,7 +5644,7 @@
         <v>0.2339622641509434</v>
       </c>
       <c r="P58">
-        <v>0.1613689194542332</v>
+        <v>0.1613689194542331</v>
       </c>
       <c r="Q58">
         <v>0.5017361111111112</v>
@@ -5741,7 +5741,7 @@
         <v>0.2672413793103448</v>
       </c>
       <c r="P59">
-        <v>0.1969762873652424</v>
+        <v>0.1969762873652419</v>
       </c>
       <c r="Q59">
         <v>0.3472222222222222</v>
@@ -5838,7 +5838,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="P60">
-        <v>0.04986997364462029</v>
+        <v>0.04986997364462021</v>
       </c>
       <c r="Q60">
         <v>0.9027777777777779</v>
@@ -5868,7 +5868,7 @@
         <v>37</v>
       </c>
       <c r="Z60">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AA60">
         <v>15</v>
@@ -5935,7 +5935,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="P61">
-        <v>0.04986997364462032</v>
+        <v>0.04986997364462023</v>
       </c>
       <c r="Q61">
         <v>0.9027777777777779</v>
@@ -6032,7 +6032,7 @@
         <v>0.2206405693950178</v>
       </c>
       <c r="P62">
-        <v>0.0245274610435954</v>
+        <v>0.0245274610435953</v>
       </c>
       <c r="Q62">
         <v>1</v>
@@ -6062,7 +6062,7 @@
         <v>39</v>
       </c>
       <c r="Z62">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA62">
         <v>1</v>
@@ -6129,7 +6129,7 @@
         <v>0.2384615384615385</v>
       </c>
       <c r="P63">
-        <v>0.3552799123856284</v>
+        <v>0.3552799123856282</v>
       </c>
       <c r="Q63">
         <v>0.6091666666666665</v>
@@ -6226,7 +6226,7 @@
         <v>0.2938388625592417</v>
       </c>
       <c r="P64">
-        <v>0.7252640270422742</v>
+        <v>0.7252640270422734</v>
       </c>
       <c r="Q64">
         <v>0.2385430839002267</v>
